--- a/data/trans_orig/IP1020-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133636</t>
+          <t>133241</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287437</t>
+          <t>286709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188116</t>
+          <t>188168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193937</t>
+          <t>193936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202858</t>
+          <t>202850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210183</t>
+          <t>210193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393754</t>
+          <t>393674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402822</t>
+          <t>402850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147101</t>
+          <t>147008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285046</t>
+          <t>285036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205170</t>
+          <t>205406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203153</t>
+          <t>203059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411556</t>
+          <t>411456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>670728</t>
+          <t>670333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>678504</t>
+          <t>678439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>710418</t>
+          <t>711119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719424</t>
+          <t>719393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1384823</t>
+          <t>1385165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396757</t>
+          <t>1396457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129334</t>
+          <t>128905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135688</t>
+          <t>135696</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146348</t>
+          <t>146349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152467</t>
+          <t>152469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278261</t>
+          <t>278667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287162</t>
+          <t>287136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202629</t>
+          <t>202781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217307</t>
+          <t>216985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414734</t>
+          <t>414535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>423473</t>
+          <t>423282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147061</t>
+          <t>147276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153368</t>
+          <t>153429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161800</t>
+          <t>161971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311236</t>
+          <t>311258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318619</t>
+          <t>318517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>17448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199543</t>
+          <t>198644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207866</t>
+          <t>207843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196515</t>
+          <t>196924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204474</t>
+          <t>204411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399204</t>
+          <t>399934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>410874</t>
+          <t>411117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>680452</t>
+          <t>681158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>694716</t>
+          <t>695228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731087</t>
+          <t>731200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>742209</t>
+          <t>742211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1416537</t>
+          <t>1415065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1434666</t>
+          <t>1433745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141375</t>
+          <t>141849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147428</t>
+          <t>147432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274266</t>
+          <t>274642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281132</t>
+          <t>281134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198756</t>
+          <t>199103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>205517</t>
+          <t>205451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217605</t>
+          <t>216934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223064</t>
+          <t>223037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418567</t>
+          <t>418205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427767</t>
+          <t>427685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150080</t>
+          <t>149819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154972</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160423</t>
+          <t>160540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165981</t>
+          <t>165976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313022</t>
+          <t>312743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320141</t>
+          <t>320036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200868</t>
+          <t>201220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206739</t>
+          <t>206735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195589</t>
+          <t>196197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203823</t>
+          <t>203985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400710</t>
+          <t>401237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409772</t>
+          <t>410409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>688933</t>
+          <t>689137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>698911</t>
+          <t>699025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725741</t>
+          <t>724890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737586</t>
+          <t>737187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1418705</t>
+          <t>1418053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433877</t>
+          <t>1433487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107843</t>
+          <t>107593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115903</t>
+          <t>115938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136229</t>
+          <t>136322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140059</t>
+          <t>140044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246252</t>
+          <t>245806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255140</t>
+          <t>255259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25321</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179690</t>
+          <t>180652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188045</t>
+          <t>188242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235201</t>
+          <t>233686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247601</t>
+          <t>247546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>420227</t>
+          <t>419252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434318</t>
+          <t>433422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14936</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174649</t>
+          <t>174506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185443</t>
+          <t>185580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176045</t>
+          <t>175662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183452</t>
+          <t>183290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355534</t>
+          <t>354976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367481</t>
+          <t>367644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158756</t>
+          <t>158747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165834</t>
+          <t>166070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169288</t>
+          <t>168703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177982</t>
+          <t>178032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331605</t>
+          <t>330544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343029</t>
+          <t>342872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>31410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>34309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59866</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>632451</t>
+          <t>633930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>649727</t>
+          <t>650597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727204</t>
+          <t>727663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744543</t>
+          <t>744859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1367446</t>
+          <t>1367639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391115</t>
+          <t>1390731</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1020-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1452</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5485</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5607</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5094</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>137274</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>133241</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>133119</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>427</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286709</t>
+          <t>287215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8785</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3157</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6995</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7152</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4634</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>207508</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203357</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>210114</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>192006</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>188168</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>193936</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>188011</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>193931</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>207508</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>202850</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>210193</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>622</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393674</t>
+          <t>394232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402850</t>
+          <t>403178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,92 +1409,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149174</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147227</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149174</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>147008</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>460</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285036</t>
+          <t>285039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,74 +1752,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4714</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3909</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3910</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4765</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206489</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>203110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>208537</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>205406</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>205405</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206489</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203059</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>577</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411456</t>
+          <t>411479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416489</t>
+          <t>416488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11189</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10688</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10536</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3307</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11581</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1076</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>716247</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>711511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>719475</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>675634</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>670333</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>678439</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>670485</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>678892</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>716247</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>711119</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>719393</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1385165</t>
+          <t>1385616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396457</t>
+          <t>1396468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6621</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3066</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7486</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7721</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2352</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6749</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>150746</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>146477</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>152466</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133325</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>128905</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>135696</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>128670</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>135687</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>150746</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>146349</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>152469</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278667</t>
+          <t>278374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287136</t>
+          <t>287126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5364</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5906</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10525</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10853</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4992</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220543</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>216613</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>199492</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>194873</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>202781</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>194545</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202383</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,12%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220543</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>216985</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414535</t>
+          <t>414597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>423282</t>
+          <t>423376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3673</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7563</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7334</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4014</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164872</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162123</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151166</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>147276</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>153429</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>147505</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153598</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>164872</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>161971</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311258</t>
+          <t>311339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318517</t>
+          <t>318724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5574</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2698</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10972</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5632</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2457</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11656</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11763</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5574</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2671</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10158</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>201508</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>196110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>204384</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204668</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>198644</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>207843</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>198537</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>207815</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201508</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>196924</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>204411</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399934</t>
+          <t>398890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411117</t>
+          <t>411045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16679</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>18278</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11700</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25770</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12126</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10473</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16942</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40005</t>
+          <t>38030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>737669</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>731463</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>742340</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>688650</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>681158</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>695228</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>680914</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>694802</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>737669</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>731200</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>742211</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1415065</t>
+          <t>1417040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433745</t>
+          <t>1433769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,92 +4617,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6419</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2275</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6227</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>145801</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>141657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>147433</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>145801</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141849</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>147432</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>379</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274642</t>
+          <t>275310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281134</t>
+          <t>281130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7643</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4326</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1796</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8144</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8373</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3349</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1322</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7425</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>221010</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>216716</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>223043</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>202921</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>199103</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>205451</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>198874</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>205466</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221010</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>216934</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>223037</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418205</t>
+          <t>418114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427685</t>
+          <t>427237</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2695</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6178</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5936</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2611</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164062</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>160648</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166005</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153302</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149819</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154942</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150061</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>155078</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>164062</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>160540</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165976</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312743</t>
+          <t>312737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320036</t>
+          <t>320179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4471</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8942</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2251</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6200</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5975</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9539</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>201265</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>196794</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>204380</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205169</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>201220</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>206735</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>201445</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>206743</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201265</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>196197</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>203985</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>562</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401237</t>
+          <t>400896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>410409</t>
+          <t>409974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7671</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9273</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5346</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15348</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>7657</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>19954</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>732138</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>724086</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>737173</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1046</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>695098</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>689137</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>699025</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>689023</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>699086</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>732138</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>724890</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>737187</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1418053</t>
+          <t>1418510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433487</t>
+          <t>1433468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4092</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9687</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124577</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>122048</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125653</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>113188</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>107593</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115938</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138922</t>
+          <t>116691</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136322</t>
+          <t>110190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140044</t>
+          <t>119549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>252111</t>
+          <t>241267</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245806</t>
+          <t>235384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255259</t>
+          <t>244464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11774</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6846</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19370</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5311</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2270</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9860</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>225432</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>217836</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>230360</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>185201</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>180652</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>188242</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>242605</t>
+          <t>179155</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233686</t>
+          <t>174346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247546</t>
+          <t>182038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>427807</t>
+          <t>404587</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>419252</t>
+          <t>396481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>433422</t>
+          <t>410324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4540</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8342</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4005</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15079</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163801</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158132</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166347</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>181243</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>174506</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>185580</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180902</t>
+          <t>147439</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175662</t>
+          <t>140828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183290</t>
+          <t>151641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>362146</t>
+          <t>311240</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354976</t>
+          <t>303807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367644</t>
+          <t>316274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6243</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2793</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4586</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1892</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12535</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163133</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158255</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166583</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>163376</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158747</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166070</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>174770</t>
+          <t>162466</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168703</t>
+          <t>157446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178032</t>
+          <t>165078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>338147</t>
+          <t>325599</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330544</t>
+          <t>319392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342872</t>
+          <t>330415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16439</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33216</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22331</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14743</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31410</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34309</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46968</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59673</t>
+          <t>59721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>676943</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>667613</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>684390</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>643009</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>633930</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>650597</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>737201</t>
+          <t>605751</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727663</t>
+          <t>595786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744859</t>
+          <t>613040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1380210</t>
+          <t>1282694</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1367639</t>
+          <t>1269941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1390731</t>
+          <t>1294250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
